--- a/stable Work/OpenManipulatorTrajectoryProject_Stable/code/trajectory_xyz.xlsx
+++ b/stable Work/OpenManipulatorTrajectoryProject_Stable/code/trajectory_xyz.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Calibration" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'XYZ_Trajectory'!$A$1:$E$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'XYZ_Trajectory'!$A$1:$E$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calibration'!$A$1:$B$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,14 +432,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,16 +474,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>181.4527144862103</v>
+        <v>181.5198201061434</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.5566986747098516</v>
+        <v>0.2784516224562071</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>41.52379073831096</v>
+        <v>42.85876837182275</v>
       </c>
     </row>
     <row r="3">
@@ -494,13 +494,13 @@
         <v>0.051</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>178.4156901829581</v>
+        <v>180.606502611762</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.8210748025814819</v>
+        <v>1.385279039952783</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>36.19663594613547</v>
+        <v>41.59654120080927</v>
       </c>
     </row>
     <row r="4">
@@ -511,13 +511,13 @@
         <v>0.101</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>175.0232551424835</v>
+        <v>179.5611324639537</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.073956171915638</v>
+        <v>2.754683848747697</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>29.33471708724878</v>
+        <v>39.83113232763912</v>
       </c>
     </row>
     <row r="5">
@@ -528,13 +528,13 @@
         <v>0.151</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>172.3966674502202</v>
+        <v>178.7320970296438</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.586783734860851</v>
+        <v>3.564748038491168</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>24.71619225363204</v>
+        <v>39.29577203791121</v>
       </c>
     </row>
     <row r="6">
@@ -545,13 +545,13 @@
         <v>0.201</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>171.0047800372038</v>
+        <v>177.710048090496</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.573972441345739</v>
+        <v>4.089830032647237</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>22.41748732338061</v>
+        <v>39.18370570872921</v>
       </c>
     </row>
     <row r="7">
@@ -562,13 +562,13 @@
         <v>0.251</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>170.4773875683208</v>
+        <v>176.3886506788939</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.569118183987467</v>
+        <v>4.059419310928897</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>21.49543073920364</v>
+        <v>38.80005777220663</v>
       </c>
     </row>
     <row r="8">
@@ -579,13 +579,13 @@
         <v>0.301</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>170.5589656150213</v>
+        <v>175.9130599698796</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1.831532568052178</v>
+        <v>5.128614362501532</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>21.73861075075655</v>
+        <v>39.19273195501881</v>
       </c>
     </row>
     <row r="9">
@@ -596,13 +596,13 @@
         <v>0.351</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>170.4530102013468</v>
+        <v>175.813700799582</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3.138053467602351</v>
+        <v>7.826235646897923</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>22.22243238463938</v>
+        <v>39.19273195501881</v>
       </c>
     </row>
     <row r="10">
@@ -613,13 +613,13 @@
         <v>0.401</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>171.1703728025461</v>
+        <v>175.6566178775981</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>5.51599057946929</v>
+        <v>10.79166108850693</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>23.14983076224951</v>
+        <v>39.19273195501881</v>
       </c>
     </row>
     <row r="11">
@@ -630,13 +630,13 @@
         <v>0.451</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>171.0475960322414</v>
+        <v>175.1760040618834</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7.877000608725213</v>
+        <v>14.00297618055902</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>23.688641746039</v>
+        <v>39.16839982647977</v>
       </c>
     </row>
     <row r="12">
@@ -647,13 +647,13 @@
         <v>0.501</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>171.306264976218</v>
+        <v>175.1360328594377</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10.52439228477867</v>
+        <v>16.70706678774907</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>24.9114686436231</v>
+        <v>39.13143323896421</v>
       </c>
     </row>
     <row r="13">
@@ -664,13 +664,13 @@
         <v>0.551</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>171.399015019874</v>
+        <v>174.7988345670898</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13.43648255970176</v>
+        <v>19.92795825917761</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>25.70254857313896</v>
+        <v>39.13143323896421</v>
       </c>
     </row>
     <row r="14">
@@ -681,13 +681,13 @@
         <v>0.601</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>171.2529912630999</v>
+        <v>173.7540869806019</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>16.6017765400278</v>
+        <v>24.14171746010404</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>26.9199348364202</v>
+        <v>38.70350568316451</v>
       </c>
     </row>
     <row r="15">
@@ -698,13 +698,13 @@
         <v>0.651</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>170.8275491486227</v>
+        <v>173.0665197315209</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>20.27200121714826</v>
+        <v>28.6643213861165</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>28.04668806789857</v>
+        <v>38.89371892292257</v>
       </c>
     </row>
     <row r="16">
@@ -715,13 +715,13 @@
         <v>0.701</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>169.4596261153197</v>
+        <v>172.5986730905505</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>23.81006312000228</v>
+        <v>33.78194267624404</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>28.5040881233009</v>
+        <v>38.88000697916854</v>
       </c>
     </row>
     <row r="17">
@@ -732,13 +732,13 @@
         <v>0.751</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>167.1618653324432</v>
+        <v>171.5461220928312</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>27.15970168791154</v>
+        <v>39.90644678562288</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>28.29245035853171</v>
+        <v>38.90395095195115</v>
       </c>
     </row>
     <row r="18">
@@ -749,13 +749,13 @@
         <v>0.801</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>165.1758450302899</v>
+        <v>170.4338228316012</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>30.49129436530133</v>
+        <v>46.60300070421662</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>28.37640521745055</v>
+        <v>39.39580933969913</v>
       </c>
     </row>
     <row r="19">
@@ -766,13 +766,13 @@
         <v>0.851</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>162.6235771871129</v>
+        <v>169.1093658514498</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>34.16704910353945</v>
+        <v>53.57356867345666</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>27.96091090334701</v>
+        <v>39.40992205373428</v>
       </c>
     </row>
     <row r="20">
@@ -783,13 +783,13 @@
         <v>0.901</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>160.3800437678381</v>
+        <v>168.2900399484554</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>37.82794883108549</v>
+        <v>59.63341855772402</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>28.01967712180874</v>
+        <v>39.41446306900534</v>
       </c>
     </row>
     <row r="21">
@@ -800,13 +800,13 @@
         <v>0.951</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>157.351896786239</v>
+        <v>167.4768208867178</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>40.69971866747909</v>
+        <v>65.1938386533657</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>27.61348917416296</v>
+        <v>38.99071482702399</v>
       </c>
     </row>
     <row r="22">
@@ -817,13 +817,13 @@
         <v>1.001</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>155.8838238543643</v>
+        <v>167.9687898253544</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>44.17044813491893</v>
+        <v>69.87699917118078</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>28.47183909428659</v>
+        <v>38.22448714333996</v>
       </c>
     </row>
     <row r="23">
@@ -834,13 +834,13 @@
         <v>1.051</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>153.8933122455574</v>
+        <v>169.4391045660363</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>47.97498241120518</v>
+        <v>73.86663125416823</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>29.79021613988166</v>
+        <v>37.16815374327459</v>
       </c>
     </row>
     <row r="24">
@@ -851,13 +851,13 @@
         <v>1.101</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>151.277361560274</v>
+        <v>171.3495673030595</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>51.52435426952165</v>
+        <v>77.21552120978805</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>29.97060739305573</v>
+        <v>34.64749673002299</v>
       </c>
     </row>
     <row r="25">
@@ -868,13 +868,13 @@
         <v>1.151</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>148.09096616051</v>
+        <v>173.6243679886489</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>55.30574001227505</v>
+        <v>79.52588848400323</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>29.71012528927076</v>
+        <v>31.08565843213088</v>
       </c>
     </row>
     <row r="26">
@@ -885,13 +885,13 @@
         <v>1.201</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>144.6774442076551</v>
+        <v>176.89355322253</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>58.88991646851421</v>
+        <v>82.0102251875044</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>28.9977020063134</v>
+        <v>27.53167239231789</v>
       </c>
     </row>
     <row r="27">
@@ -902,13 +902,13 @@
         <v>1.251</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>141.8383894303696</v>
+        <v>181.080972701933</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>62.35271374706779</v>
+        <v>84.28929264125742</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>28.90286789605278</v>
+        <v>24.63143953183871</v>
       </c>
     </row>
     <row r="28">
@@ -919,13 +919,13 @@
         <v>1.301</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>139.3084468090294</v>
+        <v>185.5597343884484</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>66.14960142043461</v>
+        <v>86.72063098923373</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>29.19908674674949</v>
+        <v>21.60024591477676</v>
       </c>
     </row>
     <row r="29">
@@ -936,13 +936,13 @@
         <v>1.351</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>136.6903326129363</v>
+        <v>190.6360597603141</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>69.06711745904775</v>
+        <v>89.44936281468996</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>29.07176226200761</v>
+        <v>19.82381024226197</v>
       </c>
     </row>
     <row r="30">
@@ -953,13 +953,13 @@
         <v>1.401</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>133.8380349866527</v>
+        <v>195.8368102219749</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>72.06674317532796</v>
+        <v>92.62380116518936</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>28.72514265610062</v>
+        <v>17.75630670004855</v>
       </c>
     </row>
     <row r="31">
@@ -970,13 +970,13 @@
         <v>1.451</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>131.4387239180066</v>
+        <v>200.475109088016</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>74.45919643110582</v>
+        <v>97.08541603900298</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>28.36186129535167</v>
+        <v>16.31137182465267</v>
       </c>
     </row>
     <row r="32">
@@ -987,13 +987,13 @@
         <v>1.501</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>128.7086120768064</v>
+        <v>205.007279773062</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>76.87680860352644</v>
+        <v>101.6201432665386</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>28.01400581677399</v>
+        <v>15.02792485729256</v>
       </c>
     </row>
     <row r="33">
@@ -1004,13 +1004,13 @@
         <v>1.551</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>125.6924814847925</v>
+        <v>208.7862003146504</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>79.59389842313483</v>
+        <v>104.6929827218692</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>27.66507875410031</v>
+        <v>13.23175947258645</v>
       </c>
     </row>
     <row r="34">
@@ -1021,13 +1021,13 @@
         <v>1.601</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>121.8104492043687</v>
+        <v>211.4431786453729</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>82.20455975040497</v>
+        <v>106.431509766519</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>27.14584001358691</v>
+        <v>10.61938213339928</v>
       </c>
     </row>
     <row r="35">
@@ -1038,13 +1038,13 @@
         <v>1.651</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>117.5900105437603</v>
+        <v>212.9613451438149</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>84.71962469128717</v>
+        <v>108.4269127153248</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>26.63371071432306</v>
+        <v>8.11162466211573</v>
       </c>
     </row>
     <row r="36">
@@ -1055,13 +1055,13 @@
         <v>1.701</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>113.0220729220476</v>
+        <v>214.0195165081066</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>86.54142743160745</v>
+        <v>109.3794026265656</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>25.73127495785951</v>
+        <v>5.174895815647972</v>
       </c>
     </row>
     <row r="37">
@@ -1072,13 +1072,13 @@
         <v>1.751</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>108.1536447105586</v>
+        <v>214.7159878925798</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>88.20542692085652</v>
+        <v>110.5674673595275</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>24.83542251136194</v>
+        <v>2.126980025172912</v>
       </c>
     </row>
     <row r="38">
@@ -1089,13 +1089,13 @@
         <v>1.801</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>103.7660954715072</v>
+        <v>215.5892875623398</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>89.78722123911349</v>
+        <v>111.0171708663738</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>23.92907273050895</v>
+        <v>-2.396786838367717</v>
       </c>
     </row>
     <row r="39">
@@ -1106,13 +1106,13 @@
         <v>1.851</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>99.66137174372417</v>
+        <v>216.2594112155551</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>91.1667475166399</v>
+        <v>112.2030008198249</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>23.01577160903366</v>
+        <v>-5.894672943339884</v>
       </c>
     </row>
     <row r="40">
@@ -1123,13 +1123,13 @@
         <v>1.901</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>96.34920376077331</v>
+        <v>217.5427523098661</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>92.58102669902003</v>
+        <v>112.8688433884684</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>22.09237081291798</v>
+        <v>-9.076808303275243</v>
       </c>
     </row>
     <row r="41">
@@ -1140,13 +1140,13 @@
         <v>1.951</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>93.28621770060828</v>
+        <v>218.4933985355109</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>93.86035460636121</v>
+        <v>113.7878042906427</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>20.97799088297856</v>
+        <v>-11.45176382393606</v>
       </c>
     </row>
     <row r="42">
@@ -1157,13 +1157,13 @@
         <v>2.001</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>89.77625113922259</v>
+        <v>218.5601367556582</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>94.5850861055944</v>
+        <v>113.8225604690157</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>19.50593496427362</v>
+        <v>-13.94507555386866</v>
       </c>
     </row>
     <row r="43">
@@ -1174,13 +1174,13 @@
         <v>2.051</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>87.30775639583932</v>
+        <v>218.250655196058</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>95.73741705919836</v>
+        <v>113.6613875119773</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>18.19641877162164</v>
+        <v>-16.49499767645443</v>
       </c>
     </row>
     <row r="44">
@@ -1191,13 +1191,13 @@
         <v>2.101</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>84.67403226335459</v>
+        <v>218.7380074122801</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>96.65181284884011</v>
+        <v>113.9151926107664</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>16.34244379055585</v>
+        <v>-18.15012691204808</v>
       </c>
     </row>
     <row r="45">
@@ -1208,13 +1208,13 @@
         <v>2.151</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>82.88479056023687</v>
+        <v>218.6544326264918</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>97.58995191451267</v>
+        <v>113.8716682231527</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>14.84447149386182</v>
+        <v>-19.66884832925848</v>
       </c>
     </row>
     <row r="46">
@@ -1225,13 +1225,13 @@
         <v>2.201</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>81.46550640805174</v>
+        <v>218.0869228417931</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>98.33966439117188</v>
+        <v>114.0017380031763</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>13.71245788839542</v>
+        <v>-20.51006915634562</v>
       </c>
     </row>
     <row r="47">
@@ -1242,13 +1242,13 @@
         <v>2.251</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>79.98918716466163</v>
+        <v>217.2115587004246</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>98.38694656890945</v>
+        <v>113.1202429763678</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>12.40726238987085</v>
+        <v>-21.02626312813396</v>
       </c>
     </row>
     <row r="48">
@@ -1259,13 +1259,13 @@
         <v>2.301</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>78.60111812225061</v>
+        <v>217.2985701586088</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>98.51843611397564</v>
+        <v>113.5896382088769</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>11.11634757984231</v>
+        <v>-20.07310714759791</v>
       </c>
     </row>
     <row r="49">
@@ -1276,13 +1276,13 @@
         <v>2.351</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>77.42414601969492</v>
+        <v>217.3167964289642</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>98.89678652384147</v>
+        <v>113.599165724194</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>10.19073015449931</v>
+        <v>-19.50283037732274</v>
       </c>
     </row>
     <row r="50">
@@ -1293,13 +1293,13 @@
         <v>2.401</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>76.05728869526756</v>
+        <v>217.1024066005816</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>99.32984542244751</v>
+        <v>113.4870965880563</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9.276938036531277</v>
+        <v>-19.12552029509749</v>
       </c>
     </row>
     <row r="51">
@@ -1310,13 +1310,13 @@
         <v>2.451</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>74.92752799099726</v>
+        <v>217.050807755531</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>100.0622916747628</v>
+        <v>113.0365265017297</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>8.909368611395678</v>
+        <v>-19.12805480258436</v>
       </c>
     </row>
     <row r="52">
@@ -1327,13 +1327,13 @@
         <v>2.501</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>73.67327282334867</v>
+        <v>216.8253720273622</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>100.2982520823777</v>
+        <v>112.9191232452061</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>8.739732271602151</v>
+        <v>-19.13019940871524</v>
       </c>
     </row>
     <row r="53">
@@ -1344,13 +1344,13 @@
         <v>2.551</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>72.3856409536365</v>
+        <v>216.2675862127014</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>100.796145024649</v>
+        <v>111.786517355693</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>8.380220317090533</v>
+        <v>-19.13487873250955</v>
       </c>
     </row>
     <row r="54">
@@ -1361,13 +1361,13 @@
         <v>2.601</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>70.75290016756308</v>
+        <v>214.775967175565</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>100.4613968596693</v>
+        <v>111.433337793834</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>7.681224913045611</v>
+        <v>-18.42297708619125</v>
       </c>
     </row>
     <row r="55">
@@ -1378,13 +1378,13 @@
         <v>2.651</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>69.76520188778657</v>
+        <v>212.0117917359228</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>100.0336933731107</v>
+        <v>109.5867404428792</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>7.161894493652426</v>
+        <v>-18.36976186953316</v>
       </c>
     </row>
     <row r="56">
@@ -1395,13 +1395,13 @@
         <v>2.701</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>68.4757100448313</v>
+        <v>208.3050053930814</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>99.80763697863107</v>
+        <v>107.6707402548512</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>6.646790131995857</v>
+        <v>-17.85960277614629</v>
       </c>
     </row>
     <row r="57">
@@ -1412,13 +1412,13 @@
         <v>2.751</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>68.16917842715054</v>
+        <v>204.6664843608119</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>100.0172504019648</v>
+        <v>105.3925003501583</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>6.646790131995857</v>
+        <v>-16.89602106820868</v>
       </c>
     </row>
     <row r="58">
@@ -1429,13 +1429,13 @@
         <v>2.801</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>67.32281436512936</v>
+        <v>201.7206164436644</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>100.0896573496215</v>
+        <v>103.8755329460467</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>6.309316991594415</v>
+        <v>-13.83276927697477</v>
       </c>
     </row>
     <row r="59">
@@ -1446,13 +1446,13 @@
         <v>2.851</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>66.6477853961477</v>
+        <v>199.2335023661959</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>100.4110473503459</v>
+        <v>102.594799698006</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>6.142769462630696</v>
+        <v>-8.088502701580182</v>
       </c>
     </row>
     <row r="60">
@@ -1463,13 +1463,13 @@
         <v>2.901</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>65.84676619804225</v>
+        <v>196.7266997685121</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>100.2020061735797</v>
+        <v>101.3039278951347</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>5.804550416426309</v>
+        <v>-1.582275714119561</v>
       </c>
     </row>
     <row r="61">
@@ -1480,13 +1480,13 @@
         <v>2.951</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>65.20182863683593</v>
+        <v>193.7734960936814</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>99.88696048505453</v>
+        <v>99.4074092769539</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>5.468222460551601</v>
+        <v>4.722169797978523</v>
       </c>
     </row>
     <row r="62">
@@ -1497,13 +1497,13 @@
         <v>3.001</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>65.04852538452413</v>
+        <v>191.3835323842497</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>99.98686252617935</v>
+        <v>97.81078280287724</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>5.468222460551601</v>
+        <v>10.22832114946505</v>
       </c>
     </row>
     <row r="63">
@@ -1514,13 +1514,13 @@
         <v>3.051</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>65.04852538452413</v>
+        <v>189.4734489175251</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>99.98686252617935</v>
+        <v>95.73745781140269</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>5.468222460551601</v>
+        <v>15.95588519171284</v>
       </c>
     </row>
     <row r="64">
@@ -1531,13 +1531,13 @@
         <v>3.101</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>64.98907533007211</v>
+        <v>188.2302284179286</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>99.89548113995224</v>
+        <v>93.30391974420323</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>21.86190735460352</v>
       </c>
     </row>
     <row r="65">
@@ -1548,13 +1548,13 @@
         <v>3.151</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>64.98907533007211</v>
+        <v>187.2133000905457</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>99.89548113995224</v>
+        <v>90.30875740001197</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>26.87394687003007</v>
       </c>
     </row>
     <row r="66">
@@ -1565,13 +1565,13 @@
         <v>3.201</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>64.83575925740156</v>
+        <v>187.9093109533333</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>99.99505680760728</v>
+        <v>87.46773702742252</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>32.38892195119979</v>
       </c>
     </row>
     <row r="67">
@@ -1582,13 +1582,13 @@
         <v>3.251</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>64.83575925740156</v>
+        <v>190.1238081867877</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>99.99505680760728</v>
+        <v>85.32515367744507</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>39.01578893487877</v>
       </c>
     </row>
     <row r="68">
@@ -1599,13 +1599,13 @@
         <v>3.301</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>64.83575925740156</v>
+        <v>191.7060608124683</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>99.99505680760728</v>
+        <v>82.5260601576925</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>45.98028225481917</v>
       </c>
     </row>
     <row r="69">
@@ -1616,13 +1616,13 @@
         <v>3.351</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>191.4664381905013</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>80.68791000262928</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>49.89702126732959</v>
       </c>
     </row>
     <row r="70">
@@ -1633,13 +1633,13 @@
         <v>3.401</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>190.7004302196196</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>78.99068629426701</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>51.46531782928764</v>
       </c>
     </row>
     <row r="71">
@@ -1650,13 +1650,13 @@
         <v>3.451</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>189.4072243771215</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>77.43575493771411</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>49.92411374162046</v>
       </c>
     </row>
     <row r="72">
@@ -1667,13 +1667,13 @@
         <v>3.501</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>187.4251776649096</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>75.95513775820633</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>47.28437624446437</v>
       </c>
     </row>
     <row r="73">
@@ -1684,13 +1684,13 @@
         <v>3.551</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>185.4889547640792</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>74.1785030978409</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>43.39796231814975</v>
       </c>
     </row>
     <row r="74">
@@ -1701,13 +1701,13 @@
         <v>3.601</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>185.3726009896431</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>71.83288734928703</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>41.51190009445551</v>
       </c>
     </row>
     <row r="75">
@@ -1718,13 +1718,13 @@
         <v>3.651</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>187.1320786746398</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>69.23250387279697</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>41.06058783200959</v>
       </c>
     </row>
     <row r="76">
@@ -1735,13 +1735,13 @@
         <v>3.701</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>187.622410964179</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>65.51354711060766</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>37.74974217910201</v>
       </c>
     </row>
     <row r="77">
@@ -1752,13 +1752,13 @@
         <v>3.751</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>188.8679520595284</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>61.43097242099655</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>34.48630505162379</v>
       </c>
     </row>
     <row r="78">
@@ -1769,13 +1769,13 @@
         <v>3.801</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>189.2504473403097</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>54.25283111120314</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>29.69113296401139</v>
       </c>
     </row>
     <row r="79">
@@ -1786,13 +1786,13 @@
         <v>3.851</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>189.9444005433272</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>46.03326581838706</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>24.54670341924137</v>
       </c>
     </row>
     <row r="80">
@@ -1803,13 +1803,13 @@
         <v>3.901</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>188.6878202127272</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>38.4357664498462</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>18.83787813015198</v>
       </c>
     </row>
     <row r="81">
@@ -1820,13 +1820,13 @@
         <v>3.951</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>64.83575925740156</v>
+        <v>186.3945988654881</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>99.99505680760728</v>
+        <v>32.04810018991633</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>13.7670754386684</v>
       </c>
     </row>
     <row r="82">
@@ -1837,13 +1837,13 @@
         <v>4.001</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>184.2974647765241</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>27.04904965178875</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>11.18832011835443</v>
       </c>
     </row>
     <row r="83">
@@ -1854,13 +1854,13 @@
         <v>4.051</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>182.5407762383782</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>22.22994787370262</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.429154900854542</v>
       </c>
     </row>
     <row r="84">
@@ -1871,13 +1871,13 @@
         <v>4.101</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>182.2361618339909</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>18.7959137693775</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.214569627212882</v>
       </c>
     </row>
     <row r="85">
@@ -1888,13 +1888,13 @@
         <v>4.151</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>182.6814071068389</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>17.42685625329595</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>10.00315512100411</v>
       </c>
     </row>
     <row r="86">
@@ -1905,13 +1905,13 @@
         <v>4.201</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>182.5762504228843</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>16.56932891595871</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>10.08054638249217</v>
       </c>
     </row>
     <row r="87">
@@ -1922,13 +1922,13 @@
         <v>4.251</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>182.1647198606868</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>16.250278129855</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>10.15979946992204</v>
       </c>
     </row>
     <row r="88">
@@ -1939,13 +1939,13 @@
         <v>4.301</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>181.8722013890816</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.94300971588775</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.787523890041911</v>
       </c>
     </row>
     <row r="89">
@@ -1956,13 +1956,13 @@
         <v>4.351</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>181.5082303243119</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.63056812021191</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.34192225495525</v>
       </c>
     </row>
     <row r="90">
@@ -1973,13 +1973,13 @@
         <v>4.401</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>181.56482752507</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.35489293263024</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.529262512683687</v>
       </c>
     </row>
     <row r="91">
@@ -1990,13 +1990,13 @@
         <v>4.451</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>181.8414589828169</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.09738398506673</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.52594864157453</v>
       </c>
     </row>
     <row r="92">
@@ -2007,13 +2007,13 @@
         <v>4.501</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>64.76066358825818</v>
+        <v>181.6344485419715</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>100.2156775917998</v>
+        <v>15.36078076495413</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>5.124514113066567</v>
+        <v>9.603057288999565</v>
       </c>
     </row>
     <row r="93">
@@ -2024,13 +2024,13 @@
         <v>4.551</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>181.0713976379667</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.59295030503706</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.422734654209506</v>
       </c>
     </row>
     <row r="94">
@@ -2041,13 +2041,13 @@
         <v>4.601</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>180.4984597578232</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>15.54361180094702</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.056783989750471</v>
       </c>
     </row>
     <row r="95">
@@ -2058,13 +2058,13 @@
         <v>4.651</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>180.4984597578232</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>15.54361180094702</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.056783989750471</v>
       </c>
     </row>
     <row r="96">
@@ -2075,13 +2075,13 @@
         <v>4.701</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>64.87920218224343</v>
+        <v>180.7516668582662</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>100.3991134131579</v>
+        <v>15.56541671207928</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>5.453997974774637</v>
+        <v>9.052300503544672</v>
       </c>
     </row>
     <row r="97">
@@ -2092,13 +2092,13 @@
         <v>4.751</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>180.7275768500014</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>15.84267134637212</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.052300503544672</v>
       </c>
     </row>
     <row r="98">
@@ -2109,13 +2109,13 @@
         <v>4.801</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>180.7030615616382</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>16.11988870039514</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.052300503544672</v>
       </c>
     </row>
     <row r="99">
@@ -2126,13 +2126,13 @@
         <v>4.851</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>180.3466756549677</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>16.08809675896221</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>8.797362044904474</v>
       </c>
     </row>
     <row r="100">
@@ -2143,13 +2143,13 @@
         <v>4.901</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>64.68229061610509</v>
+        <v>180.7030615616382</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>100.0943971713405</v>
+        <v>16.11988870039514</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>5.303839549847595</v>
+        <v>9.052300503544672</v>
       </c>
     </row>
     <row r="101">
@@ -2157,54 +2157,20 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>4.951</v>
+        <v>4.917</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>64.6229457652239</v>
+        <v>180.7030615616382</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>100.0025623427098</v>
+        <v>16.11988870039514</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>5.139516890702566</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" s="2" t="n">
-        <v>5.001</v>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v>64.6229457652239</v>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>100.0025623427098</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>5.139516890702566</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>101</v>
-      </c>
-      <c r="B103" s="2" t="n">
-        <v>5.016</v>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v>64.6229457652239</v>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>100.0025623427098</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>5.139516890702566</v>
+        <v>9.052300503544672</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E103"/>
+  <autoFilter ref="A1:E101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
